--- a/Bangalore-December-2025.xlsx
+++ b/Bangalore-December-2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="91">
   <si>
     <t>Sr. No</t>
   </si>
@@ -94,6 +94,9 @@
     <t>Profit %</t>
   </si>
   <si>
+    <t>Unnamed: 26</t>
+  </si>
+  <si>
     <t>Bangalore</t>
   </si>
   <si>
@@ -214,22 +217,22 @@
     <t>BALENO</t>
   </si>
   <si>
-    <t>Celerio</t>
-  </si>
-  <si>
-    <t>Crysta</t>
-  </si>
-  <si>
-    <t>Dzire</t>
-  </si>
-  <si>
-    <t>Fortuner</t>
+    <t>CELERIO</t>
+  </si>
+  <si>
+    <t>CRYSTA</t>
+  </si>
+  <si>
+    <t>DZIRE</t>
+  </si>
+  <si>
+    <t>FORTUNER</t>
   </si>
   <si>
     <t>HYCROSS</t>
   </si>
   <si>
-    <t>MG EVS</t>
+    <t>MG ZS EV</t>
   </si>
   <si>
     <t>SWIFT</t>
@@ -259,28 +262,31 @@
     <t>19/11/2019</t>
   </si>
   <si>
+    <t>23/03/2021</t>
+  </si>
+  <si>
+    <t>13/11/2025</t>
+  </si>
+  <si>
+    <t>17/02/2025</t>
+  </si>
+  <si>
+    <t>28/02/2024</t>
+  </si>
+  <si>
+    <t>23/02/2023</t>
+  </si>
+  <si>
+    <t>23/03/2023</t>
+  </si>
+  <si>
+    <t>31/03/2023</t>
+  </si>
+  <si>
+    <t>30/07/2024</t>
+  </si>
+  <si>
     <t>-</t>
-  </si>
-  <si>
-    <t>13/11/2025</t>
-  </si>
-  <si>
-    <t>17/02/2025</t>
-  </si>
-  <si>
-    <t>28/02/2024</t>
-  </si>
-  <si>
-    <t>23/02/2023</t>
-  </si>
-  <si>
-    <t>23/03/2023</t>
-  </si>
-  <si>
-    <t>31/03/2023</t>
-  </si>
-  <si>
-    <t>30/07/2024</t>
   </si>
 </sst>
 </file>
@@ -642,10 +648,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z38"/>
+  <dimension ref="A1:AA38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:27">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -724,25 +730,28 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:27">
       <c r="A2">
         <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2">
         <v>2025</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G2" s="2">
         <v>45235</v>
@@ -805,24 +814,24 @@
         <v>-45.64</v>
       </c>
     </row>
-    <row r="3" spans="1:26">
+    <row r="3" spans="1:27">
       <c r="A3">
         <v>24</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3">
         <v>2025</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G3" s="2">
         <v>45174</v>
@@ -885,24 +894,24 @@
         <v>25.86</v>
       </c>
     </row>
-    <row r="4" spans="1:26">
+    <row r="4" spans="1:27">
       <c r="A4">
         <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4">
         <v>2025</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G4" s="2">
         <v>43560</v>
@@ -965,27 +974,27 @@
         <v>47.88</v>
       </c>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5" spans="1:27">
       <c r="A5">
         <v>26</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5">
         <v>2025</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H5">
         <v>180620</v>
@@ -1045,27 +1054,27 @@
         <v>43.39</v>
       </c>
     </row>
-    <row r="6" spans="1:26">
+    <row r="6" spans="1:27">
       <c r="A6">
         <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6">
         <v>2025</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H6">
         <v>128908</v>
@@ -1125,27 +1134,27 @@
         <v>53.34</v>
       </c>
     </row>
-    <row r="7" spans="1:26">
+    <row r="7" spans="1:27">
       <c r="A7">
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7">
         <v>2025</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H7">
         <v>91343</v>
@@ -1205,24 +1214,24 @@
         <v>58.6</v>
       </c>
     </row>
-    <row r="8" spans="1:26">
+    <row r="8" spans="1:27">
       <c r="A8">
         <v>29</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8">
         <v>2025</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G8" s="2">
         <v>44387</v>
@@ -1285,27 +1294,27 @@
         <v>52.5</v>
       </c>
     </row>
-    <row r="9" spans="1:26">
+    <row r="9" spans="1:27">
       <c r="A9">
         <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9">
         <v>2025</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H9">
         <v>83883</v>
@@ -1365,24 +1374,24 @@
         <v>34.55</v>
       </c>
     </row>
-    <row r="10" spans="1:26">
+    <row r="10" spans="1:27">
       <c r="A10">
         <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10">
         <v>2025</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G10" s="2">
         <v>44257</v>
@@ -1445,24 +1454,24 @@
         <v>39.56</v>
       </c>
     </row>
-    <row r="11" spans="1:26">
+    <row r="11" spans="1:27">
       <c r="A11">
         <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D11">
         <v>2025</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G11" s="2">
         <v>44387</v>
@@ -1525,24 +1534,24 @@
         <v>56.34</v>
       </c>
     </row>
-    <row r="12" spans="1:26">
+    <row r="12" spans="1:27">
       <c r="A12">
         <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12">
         <v>2025</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G12" s="2">
         <v>45634</v>
@@ -1602,27 +1611,27 @@
         <v>-56303</v>
       </c>
       <c r="Z12" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
-    <row r="13" spans="1:26">
+    <row r="13" spans="1:27">
       <c r="A13">
         <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D13">
         <v>2025</v>
       </c>
       <c r="E13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G13" s="2">
         <v>45147</v>
@@ -1685,24 +1694,24 @@
         <v>10.7</v>
       </c>
     </row>
-    <row r="14" spans="1:26">
+    <row r="14" spans="1:27">
       <c r="A14">
         <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D14">
         <v>2025</v>
       </c>
       <c r="E14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G14" s="2">
         <v>44746</v>
@@ -1765,27 +1774,27 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="15" spans="1:26">
+    <row r="15" spans="1:27">
       <c r="A15">
         <v>36</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D15">
         <v>2025</v>
       </c>
       <c r="E15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H15">
         <v>68190</v>
@@ -1845,27 +1854,27 @@
         <v>76.89</v>
       </c>
     </row>
-    <row r="16" spans="1:26">
+    <row r="16" spans="1:27">
       <c r="A16">
         <v>37</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D16">
         <v>2025</v>
       </c>
       <c r="E16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H16">
         <v>65236</v>
@@ -1930,19 +1939,19 @@
         <v>38</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D17">
         <v>2025</v>
       </c>
       <c r="E17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G17" s="2">
         <v>44629</v>
@@ -2010,22 +2019,22 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D18">
         <v>2025</v>
       </c>
       <c r="E18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H18">
         <v>25710</v>
@@ -2090,19 +2099,19 @@
         <v>40</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19">
         <v>2025</v>
       </c>
       <c r="E19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F19" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G19" s="2">
         <v>44629</v>
@@ -2170,22 +2179,22 @@
         <v>41</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D20">
         <v>2025</v>
       </c>
       <c r="E20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F20" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G20" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H20">
         <v>65734</v>
@@ -2250,22 +2259,22 @@
         <v>42</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D21">
         <v>2025</v>
       </c>
       <c r="E21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F21" t="s">
-        <v>67</v>
-      </c>
-      <c r="G21" t="s">
-        <v>81</v>
+        <v>68</v>
+      </c>
+      <c r="G21" s="2">
+        <v>44350</v>
       </c>
       <c r="H21">
         <v>89921</v>
@@ -2330,22 +2339,22 @@
         <v>43</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D22">
         <v>2025</v>
       </c>
       <c r="E22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F22" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G22" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H22">
         <v>93469</v>
@@ -2402,7 +2411,7 @@
         <v>0</v>
       </c>
       <c r="Z22" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:26">
@@ -2410,22 +2419,22 @@
         <v>44</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D23">
         <v>2025</v>
       </c>
       <c r="E23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F23" t="s">
-        <v>67</v>
-      </c>
-      <c r="G23" t="s">
-        <v>81</v>
+        <v>68</v>
+      </c>
+      <c r="G23" s="2">
+        <v>44652</v>
       </c>
       <c r="H23">
         <v>40291</v>
@@ -2490,19 +2499,19 @@
         <v>45</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C24" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D24">
         <v>2025</v>
       </c>
       <c r="E24" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F24" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G24" s="2">
         <v>44628</v>
@@ -2570,19 +2579,19 @@
         <v>46</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D25">
         <v>2025</v>
       </c>
       <c r="E25" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F25" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G25" s="2">
         <v>45570</v>
@@ -2650,19 +2659,19 @@
         <v>47</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C26" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D26">
         <v>2025</v>
       </c>
       <c r="E26" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G26" s="2">
         <v>45083</v>
@@ -2730,22 +2739,22 @@
         <v>48</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D27">
         <v>2025</v>
       </c>
       <c r="E27" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F27" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G27" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H27">
         <v>365</v>
@@ -2810,22 +2819,22 @@
         <v>49</v>
       </c>
       <c r="B28" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C28" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D28">
         <v>2025</v>
       </c>
       <c r="E28" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F28" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G28" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H28">
         <v>11826</v>
@@ -2882,7 +2891,7 @@
         <v>-4733</v>
       </c>
       <c r="Z28" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29" spans="1:26">
@@ -2890,19 +2899,19 @@
         <v>50</v>
       </c>
       <c r="B29" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C29" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D29">
         <v>2025</v>
       </c>
       <c r="E29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F29" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G29" s="2">
         <v>45174</v>
@@ -2970,22 +2979,22 @@
         <v>51</v>
       </c>
       <c r="B30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C30" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D30">
         <v>2025</v>
       </c>
       <c r="E30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F30" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G30" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H30">
         <v>62172</v>
@@ -3050,22 +3059,22 @@
         <v>52</v>
       </c>
       <c r="B31" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C31" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D31">
         <v>2025</v>
       </c>
       <c r="E31" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F31" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G31" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H31">
         <v>79110</v>
@@ -3130,22 +3139,22 @@
         <v>53</v>
       </c>
       <c r="B32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C32" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D32">
         <v>2025</v>
       </c>
       <c r="E32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G32" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H32">
         <v>45097</v>
@@ -3210,22 +3219,22 @@
         <v>54</v>
       </c>
       <c r="B33" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C33" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D33">
         <v>2025</v>
       </c>
       <c r="E33" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F33" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G33" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H33">
         <v>114146</v>
@@ -3290,22 +3299,22 @@
         <v>55</v>
       </c>
       <c r="B34" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C34" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D34">
         <v>2025</v>
       </c>
       <c r="E34" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F34" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G34" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H34">
         <v>129349</v>
@@ -3370,22 +3379,22 @@
         <v>56</v>
       </c>
       <c r="B35" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C35" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D35">
         <v>2025</v>
       </c>
       <c r="E35" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F35" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G35" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H35">
         <v>1385</v>
@@ -3450,22 +3459,22 @@
         <v>57</v>
       </c>
       <c r="B36" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C36" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D36">
         <v>2025</v>
       </c>
       <c r="E36" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F36" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G36" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H36">
         <v>135296</v>
@@ -3530,22 +3539,22 @@
         <v>58</v>
       </c>
       <c r="B37" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C37" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D37">
         <v>2025</v>
       </c>
       <c r="E37" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F37" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G37" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H37">
         <v>43377</v>
@@ -3610,19 +3619,19 @@
         <v>59</v>
       </c>
       <c r="B38" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C38" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D38">
         <v>2025</v>
       </c>
       <c r="E38" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F38" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G38" s="2">
         <v>45174</v>
